--- a/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22718</t>
+          <t>22712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>41264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>28452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>39500</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56842</t>
+          <t>57607</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72780</t>
+          <t>72471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35114</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43091</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61206</t>
+          <t>62120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32773</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45455</t>
+          <t>45415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34390</t>
+          <t>34968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46964</t>
+          <t>47226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71614</t>
+          <t>70700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89729</t>
+          <t>88548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56020</t>
+          <t>56568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48922</t>
+          <t>48539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36628</t>
+          <t>36629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76580</t>
+          <t>76032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93808</t>
+          <t>94027</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>33110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>50563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51233</t>
+          <t>50798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>47324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58887</t>
+          <t>59302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90148</t>
+          <t>89006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106927</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>16161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19616</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33930</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>33797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64999</t>
+          <t>64717</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79313</t>
+          <t>79092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34308</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51077</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36419</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53366</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77051</t>
+          <t>76041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100449</t>
+          <t>99483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76338</t>
+          <t>75652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57420</t>
+          <t>56917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>74367</t>
+          <t>73451</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120984</t>
+          <t>121950</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>144382</t>
+          <t>145392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>32753</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48094</t>
+          <t>47533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60387</t>
+          <t>61102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82211</t>
+          <t>82008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51324</t>
+          <t>51264</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>65780</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48483</t>
+          <t>49044</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64404</t>
+          <t>63824</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>104534</t>
+          <t>104737</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126358</t>
+          <t>125643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>160825</t>
+          <t>161434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>194731</t>
+          <t>195904</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>172522</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206363</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>344083</t>
+          <t>343708</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>397200</t>
+          <t>389694</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>308628</t>
+          <t>307455</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>342534</t>
+          <t>341925</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>322186</t>
+          <t>321361</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>356027</t>
+          <t>357717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>634708</t>
+          <t>642214</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>687825</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>15240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22154</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,52%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10228</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17597</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>26189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41403</t>
+          <t>41407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34512</t>
+          <t>33769</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37127</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54138</t>
+          <t>53977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>41944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24374</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59134</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76145</t>
+          <t>75329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27400</t>
+          <t>27929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46148</t>
+          <t>47015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37449</t>
+          <t>37057</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48063</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66499</t>
+          <t>65632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83070</t>
+          <t>82275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26573</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34174</t>
+          <t>34753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>33633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70978</t>
+          <t>70399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,95%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17444</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>14613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>26070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27512</t>
+          <t>28060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36066</t>
+          <t>36512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>35179</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30582</t>
+          <t>30508</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>40883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58009</t>
+          <t>57563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>74017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>27749</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43902</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38050</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54846</t>
+          <t>54211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>76597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72802</t>
+          <t>72570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>88959</t>
+          <t>88955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83727</t>
+          <t>83530</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>99967</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>161701</t>
+          <t>161883</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>183634</t>
+          <t>184269</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>26497</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>42405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>34975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52239</t>
+          <t>53197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65534</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88328</t>
+          <t>88863</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73906</t>
+          <t>73134</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89303</t>
+          <t>89042</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78229</t>
+          <t>77271</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94685</t>
+          <t>95493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>157679</t>
+          <t>157144</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>180473</t>
+          <t>180134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>148578</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>181319</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>165504</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>200904</t>
+          <t>202389</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>323044</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>370197</t>
+          <t>373546</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>296348</t>
+          <t>295646</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>330942</t>
+          <t>328387</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>337877</t>
+          <t>336392</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>375104</t>
+          <t>373277</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>645549</t>
+          <t>642200</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>693180</t>
+          <t>692702</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19876</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18004</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>30455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46305</t>
+          <t>46185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25510</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>35491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33990</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51075</t>
+          <t>51195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67068</t>
+          <t>66925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>31822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23658</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>45085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65052</t>
+          <t>64126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>38880</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52667</t>
+          <t>51983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>43049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85645</t>
+          <t>86571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105413</t>
+          <t>105612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25894</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9486</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21542</t>
+          <t>21243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26200</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32219</t>
+          <t>33173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>45243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>44934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56691</t>
+          <t>55972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80421</t>
+          <t>81231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98089</t>
+          <t>98060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>22114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>28377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46826</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>22999</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>19273</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>30847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45937</t>
+          <t>45149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61616</t>
+          <t>61010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>27739</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>28480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40009</t>
+          <t>40151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>52433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>25002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26281</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33911</t>
+          <t>33637</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45695</t>
+          <t>45284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48536</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44213</t>
+          <t>44874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63273</t>
+          <t>64310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>87998</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68229</t>
+          <t>68449</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84851</t>
+          <t>84552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74910</t>
+          <t>74249</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>90613</t>
+          <t>90934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>149622</t>
+          <t>147890</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>172615</t>
+          <t>171578</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>28509</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44125</t>
+          <t>44410</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32538</t>
+          <t>33087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>50497</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65970</t>
+          <t>66297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90963</t>
+          <t>90580</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85528</t>
+          <t>85243</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101280</t>
+          <t>101144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88740</t>
+          <t>88726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>106685</t>
+          <t>106136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>177913</t>
+          <t>178296</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>202906</t>
+          <t>202579</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>189092</t>
+          <t>189234</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>171826</t>
+          <t>171223</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>209631</t>
+          <t>207722</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>333531</t>
+          <t>334332</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387098</t>
+          <t>382916</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>336298</t>
+          <t>336156</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>372652</t>
+          <t>370871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>361402</t>
+          <t>363311</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>399207</t>
+          <t>399810</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>709325</t>
+          <t>713507</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>762892</t>
+          <t>762091</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41289</t>
+          <t>42191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64937</t>
+          <t>64224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>52594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67844</t>
+          <t>67542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99832</t>
+          <t>102138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127996</t>
+          <t>129535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52816</t>
+          <t>50510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111623</t>
+          <t>111824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123906</t>
+          <t>123864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114235</t>
+          <t>115027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124540</t>
+          <t>124764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>230436</t>
+          <t>229750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245808</t>
+          <t>245481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55925</t>
+          <t>55701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58990</t>
+          <t>58038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65251</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110384</t>
+          <t>110077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119515</t>
+          <t>119855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53637</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64181</t>
+          <t>64657</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61394</t>
+          <t>61291</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73729</t>
+          <t>73749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119469</t>
+          <t>118975</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135987</t>
+          <t>136064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>16972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28809</t>
+          <t>29303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>30724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39553</t>
+          <t>39550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66905</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73480</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44545</t>
+          <t>44880</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46518</t>
+          <t>46603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53698</t>
+          <t>53677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88090</t>
+          <t>87881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97141</t>
+          <t>97229</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100152</t>
+          <t>100584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>115276</t>
+          <t>115070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,47 +12775,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>80,79%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>92,42%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>134293</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>125490</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>141792</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>86,08%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>80,44%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>92,59%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>134293</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>125015</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>140858</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>86,08%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>231671</t>
+          <t>231954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253521</t>
+          <t>253213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,49 +12888,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>19,21%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>21719</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>30522</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>19,56%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>21719</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>15154</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>30997</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>44</t>
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26999</t>
+          <t>27307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48849</t>
+          <t>48566</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89946</t>
+          <t>89432</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106264</t>
+          <t>106165</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110165</t>
+          <t>109937</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129449</t>
+          <t>128327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>203673</t>
+          <t>205758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>229951</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>27346</t>
+          <t>28468</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>46858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>58857</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84741</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>548406</t>
+          <t>549921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>588993</t>
+          <t>590002</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>637741</t>
+          <t>637030</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>674181</t>
+          <t>673605</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1198846</t>
+          <t>1200986</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1254226</t>
+          <t>1252460</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77162</t>
+          <t>76153</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117749</t>
+          <t>116234</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124231</t>
+          <t>124942</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>173901</t>
+          <t>175667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>229281</t>
+          <t>227141</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
